--- a/data/waveBoss.xlsx
+++ b/data/waveBoss.xlsx
@@ -1204,7 +1204,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -1213,7 +1213,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -1230,7 +1230,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1238,7 +1238,7 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -1247,7 +1247,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1255,7 +1255,7 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -1264,7 +1264,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1272,7 +1272,7 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
@@ -1281,7 +1281,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1289,7 +1289,7 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -1298,7 +1298,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1306,7 +1306,7 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -1315,7 +1315,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
